--- a/data/availability/projects/sodic/v-editions.xlsx
+++ b/data/availability/projects/sodic/v-editions.xlsx
@@ -657,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -966,120 +966,6 @@
         </is>
       </c>
       <c r="M5" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>v-editions</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Finished</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Landscape &amp; City View</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Ready / 2027</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>5% down · 7–8 years equal installments</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>v-editions</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1367.0</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Finished</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Landscape &amp; City View</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Ready / 2027</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>5% down · 7–8 years equal installments</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
